--- a/data/backend/static/excel_data/2762e089-7048-4e91-a408-2756419530e1/2762e089-7048-4e91-a408-2756419530e1_合并_20251225_135319.xlsx
+++ b/data/backend/static/excel_data/2762e089-7048-4e91-a408-2756419530e1/2762e089-7048-4e91-a408-2756419530e1_合并_20251225_135319.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P005_监管并表关键审慎监管指标" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P006_2024年度资本管理相关数据" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P006_2024年度资本管理相关数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P005_监管并表关键审慎监管指标" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,29 +414,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
       <c r="B1" t="inlineStr">
         <is>
-          <t>a&gt;&gt;2024年12月31日</t>
+          <t>2024年&gt;&gt;12月31日</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>b&gt;&gt;2024年9月30日</t>
+          <t>2024年&gt;&gt;9月30日</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>c&gt;&gt;2024年6月30日</t>
+          <t>2024年&gt;&gt;6月30日</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>d&gt;&gt;2024年3月31日</t>
+          <t>2024年&gt;&gt;3月31日</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -473,22 +472,22 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024年 12 月 31日</t>
+          <t>2024年 12 月 31 日</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024 年 9 月 30 日</t>
+          <t>2024年 9 月 30日</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024 年 6 月 30 日</t>
+          <t>2024年 6 月 30日</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024 年 3 月 31 日</t>
+          <t>2024年 3 月 31日</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -496,38 +495,59 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>调整后表内外资产余额</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>42,755,544</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>42,815,730</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>42,314,726</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>41,837,451</t>
+        </is>
+      </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>可用资本(数额)&gt;&gt;核心一级资本净额</t>
+          <t>杠杆率(%)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3,165,549</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3,124,043</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3,038,387</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3,045,754</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -537,27 +557,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>可用资本(数额)&gt;&gt;一级资本净额</t>
+          <t>杠杆率a(%)1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3,324,424</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3,322,954</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3,237,254</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3,245,824</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -567,27 +587,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>可用资本(数额)&gt;&gt;资本净额</t>
+          <t>杠杆率b(%)2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4,303,263</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4,285,564</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4,175,087</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4,175,290</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -595,68 +615,64 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>杠杆率c(%)3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7.65</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7.73</t>
+        </is>
+      </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="F9" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>风险加权资产(数额)&gt;&gt;风险加权资产合计</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>21,854,590</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>22,150,555</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>21,690,492</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>21,586,165</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>风险加权资产(数额)&gt;&gt;风险加权资产合计(应用资本底线前)</t>
+          <t>合格优质流动性资产</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21,854,590</t>
+          <t>6,237,408</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22,150,555</t>
+          <t>6,148,940</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21,690,492</t>
+          <t>6,115,852</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21,586,165</t>
+          <t>6,059,382</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -664,38 +680,59 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>现金净流出量</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4,957,733</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5,119,129</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4,877,791</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4,510,003</t>
+        </is>
+      </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>资本充足率&gt;&gt;核心一级资本充足率(%)</t>
+          <t>流动性覆盖率(%)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>125.73</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>120.29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>125.43</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>134.46</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -703,59 +740,34 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>资本充足率&gt;&gt;核心一级资本充足率(%)(应用资本底线前)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>14.10</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
-      </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>资本充足率&gt;&gt;一级资本充足率(%)</t>
+          <t>可用稳定资金合计</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>28,158,322</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>28,350,638</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>28,236,945</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15.04</t>
+          <t>28,350,972</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -765,27 +777,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>资本充足率&gt;&gt;一级资本充足率(%)(应用资本底线前)</t>
+          <t>所需稳定资金合计</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>21,027,700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>20,928,125</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>20,917,739</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15.04</t>
+          <t>22,174,688</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -795,27 +807,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>资本充足率&gt;&gt;资本充足率(%)</t>
+          <t>净稳定资金比例(%)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>133.91</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>135.47</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>134.99</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>127.85</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -825,220 +837,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>资本充足率&gt;&gt;资本充足率(%)(应用资本底线前)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>19.35</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>19.34</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>其他各级资本要求&gt;&gt;储备资本要求(%)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>其他各级资本要求&gt;&gt;逆周期资本要求(%)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>其他各级资本要求&gt;&gt;全球系统重要性银行或国内系统重要性银行附加资本要求(%)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>其他各级资本要求&gt;&gt;其他各级资本要求(%)(8+9+10)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>其他各级资本要求&gt;&gt;满足最低资本要求后的可用核心一级资本净额占风险加权资产的比例(%)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>9.21</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>8.92</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>9.04</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
           <t>列标记</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记说明:0-纯文本 1-标准数值 2-格式问题 3-可能错误 4-混合类型</t>
         </is>
@@ -1055,458 +869,3410 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>字段名</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;12月31日</t>
+          <t>银行名</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;9月30日</t>
+          <t>表名</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;6月30日</t>
+          <t>页号</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;3月31日</t>
+          <t>主体</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>纵向层级路径</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>横向层级路径</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>数据类型</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>币种</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>报告期</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>行标记</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>备注特征</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>记录1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>中国建设银行</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>P005_监管并表关键审慎监管指标</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>可用资本(数额)&gt;&gt;核心一级资本净额</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>万元</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>316554900000</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>记录2</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024年 12 月 31 日</t>
+          <t>中国建设银行</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024年 9 月 30日</t>
+          <t>P005_监管并表关键审慎监管指标</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024年 6 月 30日</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024年 3 月 31日</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>可用资本(数额)&gt;&gt;核心一级资本净额</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3124043</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>调整后表内外资产余额</t>
+          <t>记录3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>42,755,544</t>
+          <t>中国建设银行</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>42,815,730</t>
+          <t>P005_监管并表关键审慎监管指标</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42,314,726</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41,837,451</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>可用资本(数额)&gt;&gt;核心一级资本净额</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>c&gt;&gt;2024年6月30日</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3038387</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>杠杆率(%)</t>
+          <t>记录4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>中国建设银行</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>P005_监管并表关键审慎监管指标</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7.76</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>可用资本(数额)&gt;&gt;核心一级资本净额</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>d&gt;&gt;2024年3月31日</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>3045754</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>杠杆率a(%)1</t>
+          <t>记录5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>中国建设银行</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>P005_监管并表关键审慎监管指标</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7.76</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>可用资本(数额)&gt;&gt;一级资本净额</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3324424</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>杠杆率b(%)2</t>
+          <t>记录6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>中国建设银行</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>P005_监管并表关键审慎监管指标</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7.73</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>可用资本(数额)&gt;&gt;一级资本净额</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3322954</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>杠杆率c(%)3</t>
+          <t>记录7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>中国建设银行</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>P005_监管并表关键审慎监管指标</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7.73</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>可用资本(数额)&gt;&gt;一级资本净额</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>c&gt;&gt;2024年6月30日</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3237254</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>记录8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>可用资本(数额)&gt;&gt;一级资本净额</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>d&gt;&gt;2024年3月31日</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3245824</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>合格优质流动性资产</t>
+          <t>记录9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6,237,408</t>
+          <t>中国建设银行</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6,148,940</t>
+          <t>P005_监管并表关键审慎监管指标</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6,115,852</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6,059,382</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>风险加权资产(数额)&gt;&gt;风险加权资产合计</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>21854590</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>现金净流出量</t>
+          <t>记录10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4,957,733</t>
+          <t>中国建设银行</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5,119,129</t>
+          <t>P005_监管并表关键审慎监管指标</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4,877,791</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4,510,003</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>风险加权资产(数额)&gt;&gt;风险加权资产合计</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>22150555</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>流动性覆盖率(%)</t>
+          <t>记录11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>125.73</t>
+          <t>中国建设银行</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>120.29</t>
+          <t>P005_监管并表关键审慎监管指标</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>125.43</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>134.46</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>风险加权资产(数额)&gt;&gt;风险加权资产合计</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>c&gt;&gt;2024年6月30日</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>21690492</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>记录12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>风险加权资产(数额)&gt;&gt;风险加权资产合计</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>d&gt;&gt;2024年3月31日</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>21586165</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>可用稳定资金合计</t>
+          <t>记录13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>28,158,322</t>
+          <t>中国建设银行</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>28,350,638</t>
+          <t>P005_监管并表关键审慎监管指标</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28,236,945</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28,350,972</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;核心一级资本充足率(%)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>14.48</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>所需稳定资金合计</t>
+          <t>记录14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21,027,700</t>
+          <t>中国建设银行</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20,928,125</t>
+          <t>P005_监管并表关键审慎监管指标</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20,917,739</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22,174,688</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;核心一级资本充足率(%)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>净稳定资金比例(%)</t>
+          <t>记录15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>133.91</t>
+          <t>中国建设银行</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>135.47</t>
+          <t>P005_监管并表关键审慎监管指标</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>134.99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>127.85</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;核心一级资本充足率(%)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>c&gt;&gt;2024年6月30日</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>14.01</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>列标记</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
+          <t>记录16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>标记说明:0-纯文本 1-标准数值 2-格式问题 3-可能错误 4-混合类型</t>
-        </is>
-      </c>
+          <t>资本充足率&gt;&gt;核心一级资本充足率(%)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>d&gt;&gt;2024年3月31日</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>记录17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;核心一级资本充足率(%)(应用资本底线前)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>14.48</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>记录18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;核心一级资本充足率(%)(应用资本底线前)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>记录19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;核心一级资本充足率(%)(应用资本底线前)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>c&gt;&gt;2024年6月30日</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>14.01</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>记录20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;核心一级资本充足率(%)(应用资本底线前)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>d&gt;&gt;2024年3月31日</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>记录21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;一级资本充足率(%)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>15.21</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>记录22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;一级资本充足率(%)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>记录23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;一级资本充足率(%)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>c&gt;&gt;2024年6月30日</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>14.92</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>记录24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;一级资本充足率(%)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>d&gt;&gt;2024年3月31日</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>15.04</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>记录25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;一级资本充足率(%)(应用资本底线前)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>15.21</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>记录26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;一级资本充足率(%)(应用资本底线前)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>记录27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;一级资本充足率(%)(应用资本底线前)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>c&gt;&gt;2024年6月30日</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>14.92</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>记录28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;一级资本充足率(%)(应用资本底线前)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>d&gt;&gt;2024年3月31日</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>15.04</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>记录29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;资本充足率(%)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>记录30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;资本充足率(%)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>19.35</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>记录31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;资本充足率(%)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>c&gt;&gt;2024年6月30日</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>记录32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>资本充足率&gt;&gt;资本充足率(%)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>d&gt;&gt;2024年3月31日</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>19.34</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>记录33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;储备资本要求(%)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>记录34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;储备资本要求(%)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>记录35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;储备资本要求(%)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>c&gt;&gt;2024年6月30日</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>记录36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;储备资本要求(%)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>d&gt;&gt;2024年3月31日</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>记录37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;逆周期资本要求(%)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>记录38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;逆周期资本要求(%)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>记录39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;逆周期资本要求(%)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>c&gt;&gt;2024年6月30日</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>记录40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;逆周期资本要求(%)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>d&gt;&gt;2024年3月31日</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>记录41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;全球系统重要性银行或国内系统重要性银行附加资本要求(%)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>记录42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;全球系统重要性银行或国内系统重要性银行附加资本要求(%)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>记录43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;全球系统重要性银行或国内系统重要性银行附加资本要求(%)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>c&gt;&gt;2024年6月30日</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>记录44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;全球系统重要性银行或国内系统重要性银行附加资本要求(%)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>d&gt;&gt;2024年3月31日</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>记录45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;其他各级资本要求(%)(8+9+10)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>记录46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;其他各级资本要求(%)(8+9+10)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>记录47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;其他各级资本要求(%)(8+9+10)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>c&gt;&gt;2024年6月30日</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>记录48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>P005_监管并表关键审慎监管指标</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>其他各级资本要求&gt;&gt;其他各级资本要求(%)(8+9+10)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>d&gt;&gt;2024年3月31日</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
